--- a/SAEN PEÑA/Julio/SAENZ_EXPENSAS-Julio.xlsx
+++ b/SAEN PEÑA/Julio/SAENZ_EXPENSAS-Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A63EF5-8F17-4C3E-BD6C-D8263AFCDA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F99DDB1-97ED-4EEF-9B7A-C0CA955C4DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>UF</t>
   </si>
@@ -210,9 +210,6 @@
     <t>CORRESPONDE A:</t>
   </si>
   <si>
-    <t>Zurich</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pago efectivo </t>
   </si>
   <si>
@@ -222,9 +219,6 @@
     <t>Domicilio : Dr melo 2958 - 8vo piso  - con cita previa</t>
   </si>
   <si>
-    <t>Poliza Nro. 001170625</t>
-  </si>
-  <si>
     <t>Mercantil Andina</t>
   </si>
   <si>
@@ -237,12 +231,6 @@
     <t>Prevision</t>
   </si>
   <si>
-    <t>Camion Villar -  Destapaciones</t>
-  </si>
-  <si>
-    <t>SAC</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
@@ -250,6 +238,9 @@
   </si>
   <si>
     <t xml:space="preserve">Período JULIO </t>
+  </si>
+  <si>
+    <t>Camion Villar -  Destapaciones 22/07</t>
   </si>
 </sst>
 </file>
@@ -1673,51 +1664,51 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="102" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1725,11 +1716,11 @@
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
       <c r="E7" s="24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F7" s="103"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1737,12 +1728,12 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="106" t="s">
         <v>12</v>
       </c>
@@ -1754,32 +1745,26 @@
       </c>
       <c r="F11" s="113"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="104" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="111">
-        <v>32362.99</v>
-      </c>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="104"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="112"/>
       <c r="D12" s="5"/>
       <c r="E12" s="49" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="50">
-        <v>437075.38143240911</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>368212.76895173313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="102" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B13" s="102" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="112">
+        <v>65</v>
+      </c>
+      <c r="C13" s="111">
         <v>35601</v>
       </c>
       <c r="D13" s="36"/>
@@ -1788,17 +1773,17 @@
       </c>
       <c r="F13" s="52">
         <f>'prorrateo '!F11</f>
-        <v>286780.71501932398</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>123127.97509600001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="104" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="104" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="112">
+        <v>61</v>
+      </c>
+      <c r="C14" s="111">
         <v>34213.629999999997</v>
       </c>
       <c r="D14" s="5"/>
@@ -1806,16 +1791,16 @@
         <v>22</v>
       </c>
       <c r="F14" s="52">
-        <f>-(C36)</f>
-        <v>-364669.3775</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <f>-(C35)</f>
+        <v>-355359.13500000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="102" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="102" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C15" s="75">
         <v>32800</v>
@@ -1823,22 +1808,22 @@
       <c r="E15" s="51"/>
       <c r="F15" s="52"/>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="107"/>
       <c r="B16" s="108"/>
       <c r="C16" s="82">
         <f>SUM(C12:C15)</f>
-        <v>134977.62</v>
+        <v>102614.63</v>
       </c>
       <c r="E16" s="53" t="s">
         <v>49</v>
       </c>
       <c r="F16" s="54">
         <f>SUM(F12:F15)</f>
-        <v>359186.71895173303</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>135981.60904773313</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="106" t="s">
         <v>23</v>
       </c>
@@ -1848,12 +1833,12 @@
       <c r="E17" s="19"/>
       <c r="F17" s="20"/>
     </row>
-    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="102" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="110" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C18" s="75">
         <f xml:space="preserve"> 51328.1+51328.1*5%</f>
@@ -1863,233 +1848,221 @@
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="102" t="s">
         <v>71</v>
       </c>
       <c r="B19" s="110"/>
       <c r="C19" s="75">
-        <f>C18/2</f>
-        <v>26947.252499999999</v>
+        <v>180000</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="102" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B20" s="110"/>
-      <c r="C20" s="75">
-        <f>80000+50000</f>
-        <v>130000</v>
+      <c r="C20" s="111">
+        <v>18850</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="102" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B21" s="110"/>
-      <c r="C21" s="112">
-        <v>18850</v>
+      <c r="C21" s="111">
+        <v>200000</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="102" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="110"/>
-      <c r="C22" s="111"/>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="107"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="82">
+        <f>SUM(C17:C21)</f>
+        <v>452744.505</v>
+      </c>
       <c r="D22" s="5"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="107"/>
-      <c r="B23" s="108"/>
-      <c r="C23" s="82">
-        <f>SUM(C17:C22)</f>
-        <v>229691.75750000001</v>
+      <c r="E22" s="5"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42">
+        <f>+C22+C16</f>
+        <v>555359.13500000001</v>
       </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="42">
-        <f>+C23+C16</f>
-        <v>364669.3775</v>
-      </c>
-      <c r="D24" s="5"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="77"/>
+      <c r="C24" s="78"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="63" t="s">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="77"/>
-      <c r="C25" s="78"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="47"/>
+    </row>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="47"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="45"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="46">
+        <v>0</v>
+      </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="45"/>
-      <c r="B28" s="44"/>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="55"/>
+      <c r="B28" s="56"/>
       <c r="C28" s="46">
         <v>0</v>
       </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="55"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="46">
-        <v>0</v>
-      </c>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="73"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="76"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="73"/>
-      <c r="B30" s="74"/>
-      <c r="C30" s="76"/>
+      <c r="B30" s="80"/>
+      <c r="C30" s="81"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="73"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="81"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="76">
+        <v>0</v>
+      </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="73"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="76">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="57" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="58"/>
-      <c r="C33" s="59">
-        <f>SUM(C28:C32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B32" s="58"/>
+      <c r="C32" s="59">
+        <f>SUM(C27:C31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="46">
-        <f>C24-C22</f>
-        <v>364669.3775</v>
-      </c>
+      <c r="C33" s="46">
+        <f>C23-C21</f>
+        <v>355359.13500000001</v>
+      </c>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="72">
+        <f>+C23</f>
+        <v>555359.13500000001</v>
+      </c>
+      <c r="E34" s="105"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="72">
-        <f>+C24</f>
-        <v>364669.3775</v>
-      </c>
-      <c r="E35" s="105"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="57" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="58"/>
-      <c r="C36" s="59">
-        <f>C34</f>
-        <v>364669.3775</v>
-      </c>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="58"/>
+      <c r="C35" s="59">
+        <f>C33</f>
+        <v>355359.13500000001</v>
+      </c>
+      <c r="E35" s="16"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="16"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D45" s="16"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="19"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="20"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="18"/>
       <c r="B57" s="18"/>
-      <c r="C57" s="20"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C57" s="18"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2111,24 +2084,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="100" t="s">
         <v>60</v>
       </c>
@@ -2146,11 +2119,11 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="65">
-        <v>396675.17749999999</v>
+        <v>555359.13500000001</v>
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="66" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de JULIO</v>
@@ -2169,7 +2142,7 @@
       <c r="K2" s="70"/>
       <c r="L2" s="71"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2207,7 +2180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2237,7 +2210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2251,11 +2224,11 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>28244.470716</v>
+        <v>59977.286838</v>
       </c>
       <c r="F5" s="75">
-        <f t="shared" ref="F5" si="0">E5</f>
-        <v>28244.470716</v>
+        <f t="shared" ref="F5:F10" si="0">E5</f>
+        <v>59977.286838</v>
       </c>
       <c r="G5" s="61">
         <f>E5-F5</f>
@@ -2270,7 +2243,7 @@
       </c>
       <c r="J5" s="31">
         <f>K1*D5</f>
-        <v>59977.286838</v>
+        <v>83970.301212000006</v>
       </c>
       <c r="K5" s="15">
         <f>K2*D5</f>
@@ -2278,10 +2251,10 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>59977.286838</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>83970.301212000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2295,26 +2268,23 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>63987.357147324001</v>
-      </c>
-      <c r="F6" s="75">
-        <f>E6</f>
-        <v>63987.357147324001</v>
-      </c>
+        <v>62238.335349750007</v>
+      </c>
+      <c r="F6" s="75"/>
       <c r="G6" s="61">
         <f t="shared" ref="G6:G8" si="1">E6-F6</f>
-        <v>0</v>
+        <v>62238.335349750007</v>
       </c>
       <c r="H6" s="64">
         <f t="shared" ref="H6:H10" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>0</v>
+        <v>5228.0201693790004</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="31">
         <f>K1*D6</f>
-        <v>62238.335349750007</v>
+        <v>87135.848281500002</v>
       </c>
       <c r="K6" s="15">
         <f>K2*D6</f>
@@ -2322,10 +2292,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>62238.335349750007</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>154602.20380062901</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2339,23 +2309,23 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>29552.085101000001</v>
+        <v>94788.473329984001</v>
       </c>
       <c r="F7" s="75"/>
       <c r="G7" s="61">
         <f t="shared" si="1"/>
-        <v>29552.085101000001</v>
+        <v>94788.473329984001</v>
       </c>
       <c r="H7" s="64">
         <f t="shared" si="2"/>
-        <v>2482.3751484840004</v>
+        <v>7962.2317597186566</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="31">
         <f>K1*D7</f>
-        <v>62754.013080500001</v>
+        <v>87857.815157000005</v>
       </c>
       <c r="K7" s="15">
         <f>K2*D7</f>
@@ -2363,10 +2333,10 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="3">J7+K7+H7+G7</f>
-        <v>94788.473329984001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>190608.52024670265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2380,23 +2350,23 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>36986.80689</v>
+        <v>118635.38381376001</v>
       </c>
       <c r="F8" s="75"/>
       <c r="G8" s="61">
         <f t="shared" si="1"/>
-        <v>36986.80689</v>
+        <v>118635.38381376001</v>
       </c>
       <c r="H8" s="64">
         <f t="shared" si="2"/>
-        <v>3106.8917787600003</v>
+        <v>9965.3722403558422</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="31">
         <f>K1*D8</f>
-        <v>78541.685144999996</v>
+        <v>109961.10873000001</v>
       </c>
       <c r="K8" s="15">
         <f>K2*D8</f>
@@ -2404,10 +2374,10 @@
       </c>
       <c r="L8" s="32">
         <f t="shared" si="3"/>
-        <v>118635.38381376001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>238561.86478411587</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2421,11 +2391,11 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>29738.887156000001</v>
+        <v>63150.688258000002</v>
       </c>
       <c r="F9" s="75">
         <f>E9</f>
-        <v>29738.887156000001</v>
+        <v>63150.688258000002</v>
       </c>
       <c r="G9" s="61">
         <f>E9-F9</f>
@@ -2440,7 +2410,7 @@
       </c>
       <c r="J9" s="31">
         <f>K1*D9</f>
-        <v>63150.688258000002</v>
+        <v>88413.174292000011</v>
       </c>
       <c r="K9" s="15">
         <f>K2*D9</f>
@@ -2448,10 +2418,10 @@
       </c>
       <c r="L9" s="32">
         <f t="shared" si="3"/>
-        <v>63150.688258000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>88413.174292000011</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2465,26 +2435,23 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>145959.83607930463</v>
-      </c>
-      <c r="F10" s="75">
-        <f>145960+'detalle y gastos'!C21</f>
-        <v>164810</v>
-      </c>
+        <v>10131.154908054625</v>
+      </c>
+      <c r="F10" s="75"/>
       <c r="G10" s="61">
         <f>E10-F10</f>
-        <v>-18850.16392069537</v>
+        <v>10131.154908054625</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>851.0170122765885</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="31">
         <f>K1*D10</f>
-        <v>70013.16882875</v>
+        <v>98020.887327499993</v>
       </c>
       <c r="K10" s="15">
         <f>K2*D10</f>
@@ -2492,10 +2459,10 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>51163.004908054631</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>109003.0592478312</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2507,19 +2474,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="4">SUM(E5:E10)</f>
-        <v>334469.44308962865</v>
+        <v>408921.32249754865</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>286780.71501932398</v>
+        <v>123127.97509600001</v>
       </c>
       <c r="G11" s="43">
         <f>SUM(G5:G10)</f>
-        <v>47688.728070304627</v>
+        <v>285793.34740154864</v>
       </c>
       <c r="H11" s="43">
         <f t="shared" ref="H11:K11" si="5">SUM(H5:H10)</f>
-        <v>5589.2669272440007</v>
+        <v>24006.641181730087</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="5"/>
@@ -2527,7 +2494,7 @@
       </c>
       <c r="J11" s="39">
         <f t="shared" si="5"/>
-        <v>396675.17749999999</v>
+        <v>555359.13500000001</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="5"/>
@@ -2535,10 +2502,10 @@
       </c>
       <c r="L11" s="43">
         <f>SUM(L5:L10)</f>
-        <v>449953.17249754863</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>865159.12358327874</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="114"/>
       <c r="B12" s="114"/>
       <c r="C12" s="114"/>
@@ -2552,10 +2519,10 @@
       <c r="K12" s="114"/>
       <c r="L12" s="114"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2572,12 +2539,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="120" t="s">
         <v>27</v>
       </c>
@@ -2588,7 +2555,7 @@
       <c r="F1" s="83"/>
       <c r="G1" s="83"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="123" t="s">
         <v>55</v>
       </c>
@@ -2601,7 +2568,7 @@
       <c r="F2" s="84"/>
       <c r="G2" s="84"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="128" t="s">
         <v>0</v>
       </c>
@@ -2624,7 +2591,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="129"/>
       <c r="B4" s="129"/>
       <c r="C4" s="129"/>
@@ -2633,7 +2600,7 @@
       <c r="F4" s="116"/>
       <c r="G4" s="116"/>
     </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="85">
         <v>1</v>
       </c>
@@ -2656,7 +2623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="85">
         <v>2</v>
       </c>
@@ -2679,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="85">
         <v>3</v>
       </c>
@@ -2702,7 +2669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="85">
         <v>4</v>
       </c>
@@ -2725,7 +2692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="85">
         <v>5</v>
       </c>
@@ -2748,7 +2715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="90">
         <v>6</v>
       </c>
@@ -2771,7 +2738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="95" t="s">
         <v>10</v>
       </c>
@@ -2790,7 +2757,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="117"/>
       <c r="B12" s="118"/>
       <c r="C12" s="118"/>

--- a/SAEN PEÑA/Julio/SAENZ_EXPENSAS-Julio.xlsx
+++ b/SAEN PEÑA/Julio/SAENZ_EXPENSAS-Julio.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F99DDB1-97ED-4EEF-9B7A-C0CA955C4DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2D2D6A-F993-4B77-BABE-FA864202D046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
     <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
+    <sheet name="prorrateo  (2)" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$36</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="73">
   <si>
     <t>UF</t>
   </si>
@@ -241,17 +242,21 @@
   </si>
   <si>
     <t>Camion Villar -  Destapaciones 22/07</t>
+  </si>
+  <si>
+    <t>PRESUPUESTO APROBADO - GASTO FLETE PROYECTADO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -1050,7 +1055,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1297,6 +1302,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2227,7 +2257,7 @@
         <v>59977.286838</v>
       </c>
       <c r="F5" s="75">
-        <f t="shared" ref="F5:F10" si="0">E5</f>
+        <f t="shared" ref="F5" si="0">E5</f>
         <v>59977.286838</v>
       </c>
       <c r="G5" s="61">
@@ -2783,4 +2813,341 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0B7803-3483-4F5E-AF3D-BAA45E718D12}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="132" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="136">
+        <v>1200000</v>
+      </c>
+      <c r="H1" s="136"/>
+      <c r="I1" s="137"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="138">
+        <v>0.1512</v>
+      </c>
+      <c r="E4" s="34">
+        <v>0</v>
+      </c>
+      <c r="F4" s="75">
+        <v>0</v>
+      </c>
+      <c r="G4" s="139">
+        <f>E4-F4</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="34">
+        <f>G$1*D4</f>
+        <v>181440</v>
+      </c>
+      <c r="I4" s="34">
+        <f>H4</f>
+        <v>181440</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="138">
+        <v>0.15690000000000001</v>
+      </c>
+      <c r="E5" s="34">
+        <v>0</v>
+      </c>
+      <c r="F5" s="75">
+        <v>0</v>
+      </c>
+      <c r="G5" s="139">
+        <f t="shared" ref="G5:G7" si="0">E5-F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="34">
+        <f>G$1*D5</f>
+        <v>188280</v>
+      </c>
+      <c r="I5" s="34">
+        <f t="shared" ref="I5:I9" si="1">H5</f>
+        <v>188280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="138">
+        <v>0.15820000000000001</v>
+      </c>
+      <c r="E6" s="34">
+        <v>0</v>
+      </c>
+      <c r="F6" s="75">
+        <v>0</v>
+      </c>
+      <c r="G6" s="139">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="34">
+        <f>G$1*D6</f>
+        <v>189840</v>
+      </c>
+      <c r="I6" s="34">
+        <f t="shared" si="1"/>
+        <v>189840</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="138">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="E7" s="34">
+        <v>0</v>
+      </c>
+      <c r="F7" s="75">
+        <v>0</v>
+      </c>
+      <c r="G7" s="139">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="34">
+        <f>G$1*D7</f>
+        <v>237600</v>
+      </c>
+      <c r="I7" s="34">
+        <f t="shared" si="1"/>
+        <v>237600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="138">
+        <v>0.15920000000000001</v>
+      </c>
+      <c r="E8" s="34">
+        <v>0</v>
+      </c>
+      <c r="F8" s="75">
+        <v>0</v>
+      </c>
+      <c r="G8" s="139">
+        <f>E8-F8</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="34">
+        <f>G$1*D8</f>
+        <v>191040</v>
+      </c>
+      <c r="I8" s="34">
+        <f t="shared" si="1"/>
+        <v>191040</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="138">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="E9" s="34">
+        <v>0</v>
+      </c>
+      <c r="F9" s="75">
+        <v>0</v>
+      </c>
+      <c r="G9" s="139">
+        <f>E9-F9</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="34">
+        <f>G$1*D9</f>
+        <v>211800</v>
+      </c>
+      <c r="I9" s="34">
+        <f t="shared" si="1"/>
+        <v>211800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="140" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="141"/>
+      <c r="C10" s="142"/>
+      <c r="D10" s="143">
+        <f>SUM(D4:D9)</f>
+        <v>1</v>
+      </c>
+      <c r="E10" s="43">
+        <f t="shared" ref="E10" si="2">SUM(E4:E9)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="43">
+        <f>SUM(F4:F9)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="43">
+        <f>SUM(G4:G9)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="144">
+        <f t="shared" ref="H10" si="3">SUM(H4:H9)</f>
+        <v>1200000</v>
+      </c>
+      <c r="I10" s="43">
+        <f>SUM(I4:I9)</f>
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="114"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I12" s="6"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="G1:H1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>